--- a/data/WP18_auswertung_parteien.xlsx
+++ b/data/WP18_auswertung_parteien.xlsx
@@ -686,13 +686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{250D5AB3-4339-4BD3-86C6-2196F352000E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E0C098C-9BF6-498C-A5F6-A88064040EDF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E82D8C45-D4FE-4418-82F3-F4E82D660854}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB9A774-084D-4991-BFAB-B73B3A725D26}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02A440B2-526F-4B46-A3E6-B29250C2C0EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA4A51BA-E5C5-4DCB-A376-C3420F1947DD}"/>
 </file>